--- a/data/sync_databases/BD_Articulos.xlsx
+++ b/data/sync_databases/BD_Articulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="1290">
   <si>
     <t>SKU</t>
   </si>
@@ -1492,6 +1492,81 @@
     <t>PP8192-05</t>
   </si>
   <si>
+    <t>11-A-5016-03</t>
+  </si>
+  <si>
+    <t>11-B-9015-01</t>
+  </si>
+  <si>
+    <t>11-C-9762-01</t>
+  </si>
+  <si>
+    <t>12-D-6047-02</t>
+  </si>
+  <si>
+    <t>12-D-6074-01</t>
+  </si>
+  <si>
+    <t>12-D-6086-05</t>
+  </si>
+  <si>
+    <t>12-D-6087-05</t>
+  </si>
+  <si>
+    <t>PP12940-01</t>
+  </si>
+  <si>
+    <t>PP12940-03</t>
+  </si>
+  <si>
+    <t>PP12940-05</t>
+  </si>
+  <si>
+    <t>PP13013-02</t>
+  </si>
+  <si>
+    <t>PP13013-04</t>
+  </si>
+  <si>
+    <t>PP13013-06</t>
+  </si>
+  <si>
+    <t>PP5975-11</t>
+  </si>
+  <si>
+    <t>11-F-9413-01</t>
+  </si>
+  <si>
+    <t>P11113-68</t>
+  </si>
+  <si>
+    <t>P17147-091</t>
+  </si>
+  <si>
+    <t>P17147-35</t>
+  </si>
+  <si>
+    <t>PP7793-59</t>
+  </si>
+  <si>
+    <t>11-E-9969-01L</t>
+  </si>
+  <si>
+    <t>11-E-9969-01R</t>
+  </si>
+  <si>
+    <t>P17149-46</t>
+  </si>
+  <si>
+    <t>P9588-83</t>
+  </si>
+  <si>
+    <t>P9588-84</t>
+  </si>
+  <si>
+    <t>PP7793-60</t>
+  </si>
+  <si>
     <t>11-6463-01-(12gacr ANSI-61) - K61 - V6-R0</t>
   </si>
   <si>
@@ -3734,6 +3809,81 @@
   </si>
   <si>
     <t>ISSIV06054</t>
+  </si>
+  <si>
+    <t>SWB02448</t>
+  </si>
+  <si>
+    <t>ISSIV00098</t>
+  </si>
+  <si>
+    <t>ISSIV00163</t>
+  </si>
+  <si>
+    <t>SWB01131</t>
+  </si>
+  <si>
+    <t>SWB02334</t>
+  </si>
+  <si>
+    <t>SWB02450</t>
+  </si>
+  <si>
+    <t>SWB02451</t>
+  </si>
+  <si>
+    <t>SWB02457</t>
+  </si>
+  <si>
+    <t>SWB02458</t>
+  </si>
+  <si>
+    <t>SWB02459</t>
+  </si>
+  <si>
+    <t>SWB02460</t>
+  </si>
+  <si>
+    <t>SWB02461</t>
+  </si>
+  <si>
+    <t>SWB02462</t>
+  </si>
+  <si>
+    <t>SWB02463</t>
+  </si>
+  <si>
+    <t>SWB02449</t>
+  </si>
+  <si>
+    <t>ISSIV03066</t>
+  </si>
+  <si>
+    <t>SWB02452</t>
+  </si>
+  <si>
+    <t>SWB02453</t>
+  </si>
+  <si>
+    <t>SWB02464</t>
+  </si>
+  <si>
+    <t>ISSIV05915</t>
+  </si>
+  <si>
+    <t>ISSIV05916</t>
+  </si>
+  <si>
+    <t>SWB02454</t>
+  </si>
+  <si>
+    <t>SWB02455</t>
+  </si>
+  <si>
+    <t>SWB02456</t>
+  </si>
+  <si>
+    <t>SWB02465</t>
   </si>
 </sst>
 </file>
@@ -4065,7 +4215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F487"/>
+  <dimension ref="A1:F512"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4093,16 +4243,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="C2" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D2" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
       <c r="E2" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -4113,19 +4263,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="C3" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D3" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="E3" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F3" t="s">
-        <v>805</v>
+        <v>830</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4133,19 +4283,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="C4" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D4" t="s">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="E4" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F4" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4153,19 +4303,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="C5" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D5" t="s">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="E5" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F5" t="s">
-        <v>807</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4173,16 +4323,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="C6" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D6" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="E6" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -4193,19 +4343,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="C7" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D7" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="E7" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F7" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4213,10 +4363,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F8" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4224,10 +4374,10 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F9" t="s">
-        <v>810</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4235,19 +4385,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="C10" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D10" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="E10" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F10" t="s">
-        <v>811</v>
+        <v>836</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4255,19 +4405,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="C11" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D11" t="s">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="E11" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F11" t="s">
-        <v>812</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4275,19 +4425,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="C12" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D12" t="s">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="E12" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F12" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4295,16 +4445,16 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="C13" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E13" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F13" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4312,16 +4462,16 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="C14" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E14" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F14" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4329,10 +4479,10 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F15" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4340,10 +4490,10 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F16" t="s">
-        <v>817</v>
+        <v>842</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4351,10 +4501,10 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F17" t="s">
-        <v>818</v>
+        <v>843</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4362,10 +4512,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F18" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4373,10 +4523,10 @@
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F19" t="s">
-        <v>820</v>
+        <v>845</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4384,10 +4534,10 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F20" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4395,10 +4545,10 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F21" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4406,10 +4556,10 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F22" t="s">
-        <v>823</v>
+        <v>848</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4417,10 +4567,10 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F23" t="s">
-        <v>824</v>
+        <v>849</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4428,10 +4578,10 @@
         <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F24" t="s">
-        <v>825</v>
+        <v>850</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4439,10 +4589,10 @@
         <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F25" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4450,10 +4600,10 @@
         <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F26" t="s">
-        <v>827</v>
+        <v>852</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4461,10 +4611,10 @@
         <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F27" t="s">
-        <v>828</v>
+        <v>853</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4472,10 +4622,10 @@
         <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F28" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4483,10 +4633,10 @@
         <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F29" t="s">
-        <v>830</v>
+        <v>855</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4494,10 +4644,10 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F30" t="s">
-        <v>831</v>
+        <v>856</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4505,10 +4655,10 @@
         <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F31" t="s">
-        <v>832</v>
+        <v>857</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4516,10 +4666,10 @@
         <v>36</v>
       </c>
       <c r="E32" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F32" t="s">
-        <v>833</v>
+        <v>858</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4527,10 +4677,10 @@
         <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F33" t="s">
-        <v>834</v>
+        <v>859</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4538,10 +4688,10 @@
         <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F34" t="s">
-        <v>835</v>
+        <v>860</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4549,10 +4699,10 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F35" t="s">
-        <v>836</v>
+        <v>861</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4560,10 +4710,10 @@
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F36" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4571,10 +4721,10 @@
         <v>41</v>
       </c>
       <c r="E37" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F37" t="s">
-        <v>838</v>
+        <v>863</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4582,10 +4732,10 @@
         <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F38" t="s">
-        <v>839</v>
+        <v>864</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4593,10 +4743,10 @@
         <v>43</v>
       </c>
       <c r="E39" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F39" t="s">
-        <v>840</v>
+        <v>865</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4604,10 +4754,10 @@
         <v>44</v>
       </c>
       <c r="E40" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F40" t="s">
-        <v>841</v>
+        <v>866</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4615,10 +4765,10 @@
         <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F41" t="s">
-        <v>842</v>
+        <v>867</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4626,10 +4776,10 @@
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F42" t="s">
-        <v>843</v>
+        <v>868</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4637,10 +4787,10 @@
         <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F43" t="s">
-        <v>844</v>
+        <v>869</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4648,10 +4798,10 @@
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F44" t="s">
-        <v>845</v>
+        <v>870</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4659,10 +4809,10 @@
         <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F45" t="s">
-        <v>846</v>
+        <v>871</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4670,10 +4820,10 @@
         <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F46" t="s">
-        <v>847</v>
+        <v>872</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4681,10 +4831,10 @@
         <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F47" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4692,10 +4842,10 @@
         <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F48" t="s">
-        <v>849</v>
+        <v>874</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4703,10 +4853,10 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F49" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4714,10 +4864,10 @@
         <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F50" t="s">
-        <v>851</v>
+        <v>876</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4725,10 +4875,10 @@
         <v>55</v>
       </c>
       <c r="E51" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F51" t="s">
-        <v>852</v>
+        <v>877</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4736,10 +4886,10 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F52" t="s">
-        <v>853</v>
+        <v>878</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4747,10 +4897,10 @@
         <v>57</v>
       </c>
       <c r="E53" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F53" t="s">
-        <v>854</v>
+        <v>879</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4758,10 +4908,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F54" t="s">
-        <v>855</v>
+        <v>880</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4769,10 +4919,10 @@
         <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F55" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4780,13 +4930,13 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E56" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F56" t="s">
-        <v>857</v>
+        <v>882</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4794,13 +4944,13 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E57" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F57" t="s">
-        <v>858</v>
+        <v>883</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4808,10 +4958,10 @@
         <v>62</v>
       </c>
       <c r="E58" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F58" t="s">
-        <v>859</v>
+        <v>884</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4819,10 +4969,10 @@
         <v>63</v>
       </c>
       <c r="E59" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F59" t="s">
-        <v>860</v>
+        <v>885</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4830,10 +4980,10 @@
         <v>64</v>
       </c>
       <c r="E60" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F60" t="s">
-        <v>861</v>
+        <v>886</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4841,10 +4991,10 @@
         <v>65</v>
       </c>
       <c r="E61" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F61" t="s">
-        <v>862</v>
+        <v>887</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -4852,10 +5002,10 @@
         <v>66</v>
       </c>
       <c r="E62" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F62" t="s">
-        <v>863</v>
+        <v>888</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -4863,10 +5013,10 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F63" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -4874,10 +5024,10 @@
         <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F64" t="s">
-        <v>865</v>
+        <v>890</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -4885,10 +5035,10 @@
         <v>69</v>
       </c>
       <c r="E65" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F65" t="s">
-        <v>866</v>
+        <v>891</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -4896,10 +5046,10 @@
         <v>70</v>
       </c>
       <c r="E66" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F66" t="s">
-        <v>867</v>
+        <v>892</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -4907,19 +5057,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="C67" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D67" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="E67" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F67" t="s">
-        <v>868</v>
+        <v>893</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -4927,10 +5077,10 @@
         <v>72</v>
       </c>
       <c r="E68" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F68" t="s">
-        <v>869</v>
+        <v>894</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4938,10 +5088,10 @@
         <v>73</v>
       </c>
       <c r="E69" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F69" t="s">
-        <v>870</v>
+        <v>895</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4949,10 +5099,10 @@
         <v>74</v>
       </c>
       <c r="E70" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F70" t="s">
-        <v>871</v>
+        <v>896</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -4960,10 +5110,10 @@
         <v>75</v>
       </c>
       <c r="E71" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F71" t="s">
-        <v>872</v>
+        <v>897</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4971,10 +5121,10 @@
         <v>76</v>
       </c>
       <c r="E72" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F72" t="s">
-        <v>873</v>
+        <v>898</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -4982,10 +5132,10 @@
         <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F73" t="s">
-        <v>874</v>
+        <v>899</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4993,10 +5143,10 @@
         <v>78</v>
       </c>
       <c r="E74" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F74" t="s">
-        <v>875</v>
+        <v>900</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5004,10 +5154,10 @@
         <v>79</v>
       </c>
       <c r="E75" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F75" t="s">
-        <v>876</v>
+        <v>901</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5015,13 +5165,13 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E76" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F76" t="s">
-        <v>877</v>
+        <v>902</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5029,13 +5179,13 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E77" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F77" t="s">
-        <v>878</v>
+        <v>903</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5043,10 +5193,10 @@
         <v>82</v>
       </c>
       <c r="E78" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F78" t="s">
-        <v>879</v>
+        <v>904</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5054,10 +5204,10 @@
         <v>83</v>
       </c>
       <c r="E79" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F79" t="s">
-        <v>880</v>
+        <v>905</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5065,10 +5215,10 @@
         <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F80" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5076,10 +5226,10 @@
         <v>85</v>
       </c>
       <c r="E81" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F81" t="s">
-        <v>882</v>
+        <v>907</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5087,10 +5237,10 @@
         <v>86</v>
       </c>
       <c r="E82" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F82" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5098,10 +5248,10 @@
         <v>87</v>
       </c>
       <c r="E83" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F83" t="s">
-        <v>884</v>
+        <v>909</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -5109,10 +5259,10 @@
         <v>88</v>
       </c>
       <c r="E84" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F84" t="s">
-        <v>885</v>
+        <v>910</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5120,10 +5270,10 @@
         <v>89</v>
       </c>
       <c r="E85" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F85" t="s">
-        <v>886</v>
+        <v>911</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5131,10 +5281,10 @@
         <v>90</v>
       </c>
       <c r="E86" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F86" t="s">
-        <v>887</v>
+        <v>912</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5142,10 +5292,10 @@
         <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F87" t="s">
-        <v>888</v>
+        <v>913</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5153,10 +5303,10 @@
         <v>92</v>
       </c>
       <c r="E88" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F88" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5164,10 +5314,10 @@
         <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F89" t="s">
-        <v>890</v>
+        <v>915</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5175,10 +5325,10 @@
         <v>94</v>
       </c>
       <c r="E90" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F90" t="s">
-        <v>891</v>
+        <v>916</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5186,10 +5336,10 @@
         <v>95</v>
       </c>
       <c r="E91" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F91" t="s">
-        <v>892</v>
+        <v>917</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -5197,10 +5347,10 @@
         <v>96</v>
       </c>
       <c r="E92" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F92" t="s">
-        <v>893</v>
+        <v>918</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5208,10 +5358,10 @@
         <v>97</v>
       </c>
       <c r="E93" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F93" t="s">
-        <v>894</v>
+        <v>919</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5219,10 +5369,10 @@
         <v>98</v>
       </c>
       <c r="E94" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F94" t="s">
-        <v>895</v>
+        <v>920</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -5230,10 +5380,10 @@
         <v>99</v>
       </c>
       <c r="E95" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F95" t="s">
-        <v>896</v>
+        <v>921</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -5241,10 +5391,10 @@
         <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F96" t="s">
-        <v>897</v>
+        <v>922</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -5252,10 +5402,10 @@
         <v>101</v>
       </c>
       <c r="E97" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F97" t="s">
-        <v>898</v>
+        <v>923</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -5263,10 +5413,10 @@
         <v>102</v>
       </c>
       <c r="E98" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F98" t="s">
-        <v>899</v>
+        <v>924</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -5274,10 +5424,10 @@
         <v>103</v>
       </c>
       <c r="E99" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F99" t="s">
-        <v>900</v>
+        <v>925</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -5285,10 +5435,10 @@
         <v>104</v>
       </c>
       <c r="E100" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F100" t="s">
-        <v>901</v>
+        <v>926</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -5296,10 +5446,10 @@
         <v>105</v>
       </c>
       <c r="E101" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F101" t="s">
-        <v>902</v>
+        <v>927</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5307,10 +5457,10 @@
         <v>106</v>
       </c>
       <c r="E102" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F102" t="s">
-        <v>903</v>
+        <v>928</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -5318,16 +5468,16 @@
         <v>107</v>
       </c>
       <c r="B103" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="C103" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D103" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="E103" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F103" t="s">
         <v>107</v>
@@ -5338,10 +5488,10 @@
         <v>108</v>
       </c>
       <c r="E104" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F104" t="s">
-        <v>904</v>
+        <v>929</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -5349,10 +5499,10 @@
         <v>109</v>
       </c>
       <c r="E105" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F105" t="s">
-        <v>905</v>
+        <v>930</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -5360,10 +5510,10 @@
         <v>110</v>
       </c>
       <c r="E106" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F106" t="s">
-        <v>906</v>
+        <v>931</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -5371,10 +5521,10 @@
         <v>111</v>
       </c>
       <c r="E107" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F107" t="s">
-        <v>907</v>
+        <v>932</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -5382,10 +5532,10 @@
         <v>112</v>
       </c>
       <c r="E108" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F108" t="s">
-        <v>908</v>
+        <v>933</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -5393,10 +5543,10 @@
         <v>113</v>
       </c>
       <c r="E109" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F109" t="s">
-        <v>909</v>
+        <v>934</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -5404,10 +5554,10 @@
         <v>114</v>
       </c>
       <c r="E110" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F110" t="s">
-        <v>910</v>
+        <v>935</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -5415,10 +5565,10 @@
         <v>115</v>
       </c>
       <c r="E111" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F111" t="s">
-        <v>911</v>
+        <v>936</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -5426,13 +5576,13 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E112" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F112" t="s">
-        <v>912</v>
+        <v>937</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5440,13 +5590,13 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E113" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F113" t="s">
-        <v>913</v>
+        <v>938</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5454,13 +5604,13 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E114" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F114" t="s">
-        <v>914</v>
+        <v>939</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5468,13 +5618,13 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E115" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F115" t="s">
-        <v>915</v>
+        <v>940</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5482,10 +5632,10 @@
         <v>120</v>
       </c>
       <c r="E116" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F116" t="s">
-        <v>916</v>
+        <v>941</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5493,13 +5643,13 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E117" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F117" t="s">
-        <v>917</v>
+        <v>942</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -5507,10 +5657,10 @@
         <v>122</v>
       </c>
       <c r="E118" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F118" t="s">
-        <v>918</v>
+        <v>943</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -5518,10 +5668,10 @@
         <v>123</v>
       </c>
       <c r="E119" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F119" t="s">
-        <v>919</v>
+        <v>944</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5529,13 +5679,13 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E120" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F120" t="s">
-        <v>920</v>
+        <v>945</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5543,13 +5693,13 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E121" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F121" t="s">
-        <v>921</v>
+        <v>946</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5557,10 +5707,10 @@
         <v>126</v>
       </c>
       <c r="E122" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F122" t="s">
-        <v>922</v>
+        <v>947</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5568,10 +5718,10 @@
         <v>127</v>
       </c>
       <c r="E123" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F123" t="s">
-        <v>923</v>
+        <v>948</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5579,10 +5729,10 @@
         <v>128</v>
       </c>
       <c r="E124" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F124" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5590,10 +5740,10 @@
         <v>129</v>
       </c>
       <c r="E125" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F125" t="s">
-        <v>925</v>
+        <v>950</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5601,10 +5751,10 @@
         <v>130</v>
       </c>
       <c r="E126" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F126" t="s">
-        <v>926</v>
+        <v>951</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5612,10 +5762,10 @@
         <v>131</v>
       </c>
       <c r="E127" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F127" t="s">
-        <v>927</v>
+        <v>952</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5623,10 +5773,10 @@
         <v>132</v>
       </c>
       <c r="E128" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F128" t="s">
-        <v>928</v>
+        <v>953</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5634,10 +5784,10 @@
         <v>133</v>
       </c>
       <c r="E129" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F129" t="s">
-        <v>929</v>
+        <v>954</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -5645,10 +5795,10 @@
         <v>134</v>
       </c>
       <c r="E130" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F130" t="s">
-        <v>930</v>
+        <v>955</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5656,13 +5806,13 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E131" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F131" t="s">
-        <v>931</v>
+        <v>956</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5670,13 +5820,13 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E132" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F132" t="s">
-        <v>932</v>
+        <v>957</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5684,13 +5834,13 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E133" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F133" t="s">
-        <v>933</v>
+        <v>958</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -5698,13 +5848,13 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E134" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F134" t="s">
-        <v>934</v>
+        <v>959</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -5712,10 +5862,10 @@
         <v>139</v>
       </c>
       <c r="E135" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F135" t="s">
-        <v>935</v>
+        <v>960</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5723,10 +5873,10 @@
         <v>140</v>
       </c>
       <c r="E136" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F136" t="s">
-        <v>936</v>
+        <v>961</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5734,13 +5884,13 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E137" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F137" t="s">
-        <v>937</v>
+        <v>962</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5748,13 +5898,13 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E138" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F138" t="s">
-        <v>938</v>
+        <v>963</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5762,13 +5912,13 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E139" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F139" t="s">
-        <v>939</v>
+        <v>964</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -5776,13 +5926,13 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E140" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F140" t="s">
-        <v>940</v>
+        <v>965</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -5790,10 +5940,10 @@
         <v>145</v>
       </c>
       <c r="E141" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F141" t="s">
-        <v>941</v>
+        <v>966</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5801,10 +5951,10 @@
         <v>146</v>
       </c>
       <c r="E142" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F142" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5812,13 +5962,13 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E143" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F143" t="s">
-        <v>943</v>
+        <v>968</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5826,13 +5976,13 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E144" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F144" t="s">
-        <v>944</v>
+        <v>969</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5840,13 +5990,13 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E145" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F145" t="s">
-        <v>945</v>
+        <v>970</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5854,13 +6004,13 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E146" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F146" t="s">
-        <v>946</v>
+        <v>971</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5868,10 +6018,10 @@
         <v>151</v>
       </c>
       <c r="E147" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F147" t="s">
-        <v>947</v>
+        <v>972</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5879,10 +6029,10 @@
         <v>152</v>
       </c>
       <c r="E148" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F148" t="s">
-        <v>948</v>
+        <v>973</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5890,13 +6040,13 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E149" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F149" t="s">
-        <v>949</v>
+        <v>974</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5904,13 +6054,13 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E150" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F150" t="s">
-        <v>950</v>
+        <v>975</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5918,13 +6068,13 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E151" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F151" t="s">
-        <v>951</v>
+        <v>976</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5932,10 +6082,10 @@
         <v>156</v>
       </c>
       <c r="E152" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F152" t="s">
-        <v>952</v>
+        <v>977</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5943,10 +6093,10 @@
         <v>157</v>
       </c>
       <c r="E153" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F153" t="s">
-        <v>953</v>
+        <v>978</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5954,10 +6104,10 @@
         <v>158</v>
       </c>
       <c r="E154" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F154" t="s">
-        <v>954</v>
+        <v>979</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5965,10 +6115,10 @@
         <v>159</v>
       </c>
       <c r="E155" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F155" t="s">
-        <v>955</v>
+        <v>980</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5976,10 +6126,10 @@
         <v>160</v>
       </c>
       <c r="E156" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F156" t="s">
-        <v>956</v>
+        <v>981</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5987,10 +6137,10 @@
         <v>161</v>
       </c>
       <c r="E157" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F157" t="s">
-        <v>957</v>
+        <v>982</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5998,10 +6148,10 @@
         <v>162</v>
       </c>
       <c r="E158" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F158" t="s">
-        <v>958</v>
+        <v>983</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -6009,10 +6159,10 @@
         <v>163</v>
       </c>
       <c r="E159" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F159" t="s">
-        <v>959</v>
+        <v>984</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -6020,10 +6170,10 @@
         <v>164</v>
       </c>
       <c r="E160" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F160" t="s">
-        <v>960</v>
+        <v>985</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -6031,13 +6181,13 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E161" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F161" t="s">
-        <v>961</v>
+        <v>986</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -6045,13 +6195,13 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E162" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F162" t="s">
-        <v>962</v>
+        <v>987</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -6059,13 +6209,13 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E163" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F163" t="s">
-        <v>963</v>
+        <v>988</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -6073,10 +6223,10 @@
         <v>168</v>
       </c>
       <c r="E164" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F164" t="s">
-        <v>964</v>
+        <v>989</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -6084,10 +6234,10 @@
         <v>169</v>
       </c>
       <c r="E165" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F165" t="s">
-        <v>965</v>
+        <v>990</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -6095,13 +6245,13 @@
         <v>170</v>
       </c>
       <c r="B166" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="E166" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F166" t="s">
-        <v>966</v>
+        <v>991</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -6109,19 +6259,19 @@
         <v>171</v>
       </c>
       <c r="B167" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="C167" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D167" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="E167" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F167" t="s">
-        <v>967</v>
+        <v>992</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -6129,19 +6279,19 @@
         <v>172</v>
       </c>
       <c r="B168" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="C168" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D168" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="E168" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F168" t="s">
-        <v>968</v>
+        <v>993</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -6149,16 +6299,16 @@
         <v>173</v>
       </c>
       <c r="B169" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="C169" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D169" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="E169" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F169" t="s">
         <v>173</v>
@@ -6169,16 +6319,16 @@
         <v>174</v>
       </c>
       <c r="B170" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="C170" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E170" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F170" t="s">
-        <v>969</v>
+        <v>994</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -6186,16 +6336,16 @@
         <v>175</v>
       </c>
       <c r="B171" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="C171" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D171" t="s">
-        <v>694</v>
+        <v>719</v>
       </c>
       <c r="E171" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F171" t="s">
         <v>175</v>
@@ -6206,16 +6356,16 @@
         <v>176</v>
       </c>
       <c r="B172" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="C172" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D172" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="E172" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F172" t="s">
         <v>176</v>
@@ -6226,10 +6376,10 @@
         <v>177</v>
       </c>
       <c r="E173" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F173" t="s">
-        <v>970</v>
+        <v>995</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -6237,10 +6387,10 @@
         <v>178</v>
       </c>
       <c r="E174" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F174" t="s">
-        <v>971</v>
+        <v>996</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -6248,10 +6398,10 @@
         <v>179</v>
       </c>
       <c r="E175" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F175" t="s">
-        <v>972</v>
+        <v>997</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -6259,10 +6409,10 @@
         <v>180</v>
       </c>
       <c r="E176" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F176" t="s">
-        <v>973</v>
+        <v>998</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6270,10 +6420,10 @@
         <v>181</v>
       </c>
       <c r="E177" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F177" t="s">
-        <v>974</v>
+        <v>999</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -6281,10 +6431,10 @@
         <v>182</v>
       </c>
       <c r="E178" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F178" t="s">
-        <v>975</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -6292,10 +6442,10 @@
         <v>183</v>
       </c>
       <c r="E179" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F179" t="s">
-        <v>976</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6303,10 +6453,10 @@
         <v>184</v>
       </c>
       <c r="E180" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F180" t="s">
-        <v>977</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -6314,10 +6464,10 @@
         <v>185</v>
       </c>
       <c r="E181" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F181" t="s">
-        <v>978</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -6325,10 +6475,10 @@
         <v>186</v>
       </c>
       <c r="E182" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F182" t="s">
-        <v>979</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6336,10 +6486,10 @@
         <v>187</v>
       </c>
       <c r="E183" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F183" t="s">
-        <v>980</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -6347,10 +6497,10 @@
         <v>188</v>
       </c>
       <c r="E184" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F184" t="s">
-        <v>981</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -6358,10 +6508,10 @@
         <v>189</v>
       </c>
       <c r="E185" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F185" t="s">
-        <v>982</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -6369,10 +6519,10 @@
         <v>190</v>
       </c>
       <c r="E186" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F186" t="s">
-        <v>983</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -6380,10 +6530,10 @@
         <v>191</v>
       </c>
       <c r="E187" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F187" t="s">
-        <v>984</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -6391,10 +6541,10 @@
         <v>192</v>
       </c>
       <c r="E188" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F188" t="s">
-        <v>985</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -6402,10 +6552,10 @@
         <v>193</v>
       </c>
       <c r="E189" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F189" t="s">
-        <v>986</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -6413,10 +6563,10 @@
         <v>194</v>
       </c>
       <c r="E190" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F190" t="s">
-        <v>987</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -6424,10 +6574,10 @@
         <v>195</v>
       </c>
       <c r="E191" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F191" t="s">
-        <v>988</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -6435,10 +6585,10 @@
         <v>196</v>
       </c>
       <c r="E192" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F192" t="s">
-        <v>989</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -6446,10 +6596,10 @@
         <v>197</v>
       </c>
       <c r="E193" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F193" t="s">
-        <v>990</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -6457,10 +6607,10 @@
         <v>198</v>
       </c>
       <c r="E194" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F194" t="s">
-        <v>991</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -6468,10 +6618,10 @@
         <v>199</v>
       </c>
       <c r="E195" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F195" t="s">
-        <v>992</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -6479,10 +6629,10 @@
         <v>200</v>
       </c>
       <c r="E196" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F196" t="s">
-        <v>993</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -6490,10 +6640,10 @@
         <v>201</v>
       </c>
       <c r="E197" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F197" t="s">
-        <v>994</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -6501,10 +6651,10 @@
         <v>202</v>
       </c>
       <c r="E198" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F198" t="s">
-        <v>995</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -6512,10 +6662,10 @@
         <v>203</v>
       </c>
       <c r="E199" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F199" t="s">
-        <v>996</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -6523,10 +6673,10 @@
         <v>204</v>
       </c>
       <c r="E200" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F200" t="s">
-        <v>997</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -6534,10 +6684,10 @@
         <v>205</v>
       </c>
       <c r="E201" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F201" t="s">
-        <v>998</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -6545,10 +6695,10 @@
         <v>206</v>
       </c>
       <c r="E202" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F202" t="s">
-        <v>999</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -6556,10 +6706,10 @@
         <v>207</v>
       </c>
       <c r="E203" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F203" t="s">
-        <v>1000</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -6567,10 +6717,10 @@
         <v>208</v>
       </c>
       <c r="E204" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F204" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -6578,10 +6728,10 @@
         <v>209</v>
       </c>
       <c r="E205" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F205" t="s">
-        <v>1002</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -6589,10 +6739,10 @@
         <v>210</v>
       </c>
       <c r="E206" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F206" t="s">
-        <v>1003</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -6600,10 +6750,10 @@
         <v>211</v>
       </c>
       <c r="E207" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F207" t="s">
-        <v>1004</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -6611,10 +6761,10 @@
         <v>212</v>
       </c>
       <c r="E208" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F208" t="s">
-        <v>1005</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -6622,10 +6772,10 @@
         <v>213</v>
       </c>
       <c r="E209" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F209" t="s">
-        <v>1006</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -6633,10 +6783,10 @@
         <v>214</v>
       </c>
       <c r="E210" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F210" t="s">
-        <v>1007</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -6644,10 +6794,10 @@
         <v>215</v>
       </c>
       <c r="E211" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F211" t="s">
-        <v>1008</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -6655,10 +6805,10 @@
         <v>216</v>
       </c>
       <c r="E212" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F212" t="s">
-        <v>1009</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -6666,10 +6816,10 @@
         <v>217</v>
       </c>
       <c r="E213" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F213" t="s">
-        <v>1010</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -6677,10 +6827,10 @@
         <v>218</v>
       </c>
       <c r="E214" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F214" t="s">
-        <v>1011</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -6688,10 +6838,10 @@
         <v>219</v>
       </c>
       <c r="E215" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F215" t="s">
-        <v>1012</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -6699,10 +6849,10 @@
         <v>220</v>
       </c>
       <c r="E216" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F216" t="s">
-        <v>1013</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -6710,10 +6860,10 @@
         <v>221</v>
       </c>
       <c r="E217" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F217" t="s">
-        <v>1014</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -6721,10 +6871,10 @@
         <v>222</v>
       </c>
       <c r="E218" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F218" t="s">
-        <v>1015</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -6732,10 +6882,10 @@
         <v>223</v>
       </c>
       <c r="E219" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F219" t="s">
-        <v>1016</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -6743,10 +6893,10 @@
         <v>224</v>
       </c>
       <c r="E220" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F220" t="s">
-        <v>1017</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -6754,10 +6904,10 @@
         <v>225</v>
       </c>
       <c r="E221" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F221" t="s">
-        <v>1018</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -6765,10 +6915,10 @@
         <v>226</v>
       </c>
       <c r="E222" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F222" t="s">
-        <v>1019</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -6776,10 +6926,10 @@
         <v>227</v>
       </c>
       <c r="E223" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F223" t="s">
-        <v>1020</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -6787,10 +6937,10 @@
         <v>228</v>
       </c>
       <c r="E224" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F224" t="s">
-        <v>1021</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -6798,10 +6948,10 @@
         <v>229</v>
       </c>
       <c r="E225" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F225" t="s">
-        <v>1022</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -6809,10 +6959,10 @@
         <v>230</v>
       </c>
       <c r="E226" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F226" t="s">
-        <v>1023</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -6820,10 +6970,10 @@
         <v>231</v>
       </c>
       <c r="E227" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F227" t="s">
-        <v>1024</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -6831,10 +6981,10 @@
         <v>232</v>
       </c>
       <c r="E228" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F228" t="s">
-        <v>1025</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -6842,10 +6992,10 @@
         <v>233</v>
       </c>
       <c r="E229" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F229" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -6853,10 +7003,10 @@
         <v>234</v>
       </c>
       <c r="E230" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F230" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -6864,10 +7014,10 @@
         <v>235</v>
       </c>
       <c r="E231" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F231" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -6875,10 +7025,10 @@
         <v>236</v>
       </c>
       <c r="E232" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F232" t="s">
-        <v>1029</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -6886,10 +7036,10 @@
         <v>237</v>
       </c>
       <c r="E233" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F233" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -6897,10 +7047,10 @@
         <v>238</v>
       </c>
       <c r="E234" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F234" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6908,10 +7058,10 @@
         <v>239</v>
       </c>
       <c r="E235" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F235" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6919,10 +7069,10 @@
         <v>240</v>
       </c>
       <c r="E236" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F236" t="s">
-        <v>1033</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6930,10 +7080,10 @@
         <v>241</v>
       </c>
       <c r="E237" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F237" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -6941,10 +7091,10 @@
         <v>242</v>
       </c>
       <c r="E238" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F238" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -6952,10 +7102,10 @@
         <v>243</v>
       </c>
       <c r="E239" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F239" t="s">
-        <v>1036</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -6963,10 +7113,10 @@
         <v>244</v>
       </c>
       <c r="E240" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F240" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -6974,10 +7124,10 @@
         <v>245</v>
       </c>
       <c r="E241" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F241" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -6985,10 +7135,10 @@
         <v>246</v>
       </c>
       <c r="E242" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F242" t="s">
-        <v>1039</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -6996,10 +7146,10 @@
         <v>247</v>
       </c>
       <c r="E243" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F243" t="s">
-        <v>1040</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -7007,10 +7157,10 @@
         <v>248</v>
       </c>
       <c r="E244" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F244" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -7018,10 +7168,10 @@
         <v>249</v>
       </c>
       <c r="E245" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F245" t="s">
-        <v>1042</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -7029,10 +7179,10 @@
         <v>250</v>
       </c>
       <c r="E246" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F246" t="s">
-        <v>1043</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -7040,10 +7190,10 @@
         <v>251</v>
       </c>
       <c r="E247" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F247" t="s">
-        <v>1044</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -7051,10 +7201,10 @@
         <v>252</v>
       </c>
       <c r="E248" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F248" t="s">
-        <v>1045</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -7062,10 +7212,10 @@
         <v>253</v>
       </c>
       <c r="E249" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F249" t="s">
-        <v>1046</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -7073,10 +7223,10 @@
         <v>254</v>
       </c>
       <c r="E250" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F250" t="s">
-        <v>1047</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -7084,10 +7234,10 @@
         <v>255</v>
       </c>
       <c r="E251" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F251" t="s">
-        <v>1048</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -7095,10 +7245,10 @@
         <v>256</v>
       </c>
       <c r="E252" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F252" t="s">
-        <v>1049</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -7106,10 +7256,10 @@
         <v>257</v>
       </c>
       <c r="E253" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F253" t="s">
-        <v>1050</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -7117,7 +7267,7 @@
         <v>258</v>
       </c>
       <c r="E254" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F254" t="s">
         <v>258</v>
@@ -7128,10 +7278,10 @@
         <v>259</v>
       </c>
       <c r="E255" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F255" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -7139,10 +7289,10 @@
         <v>260</v>
       </c>
       <c r="E256" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F256" t="s">
-        <v>1052</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7150,10 +7300,10 @@
         <v>261</v>
       </c>
       <c r="E257" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F257" t="s">
-        <v>1053</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -7161,10 +7311,10 @@
         <v>262</v>
       </c>
       <c r="E258" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F258" t="s">
-        <v>1054</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -7172,10 +7322,10 @@
         <v>263</v>
       </c>
       <c r="E259" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F259" t="s">
-        <v>1055</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7183,10 +7333,10 @@
         <v>264</v>
       </c>
       <c r="E260" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F260" t="s">
-        <v>1056</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -7194,10 +7344,10 @@
         <v>265</v>
       </c>
       <c r="E261" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F261" t="s">
-        <v>1057</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7205,10 +7355,10 @@
         <v>266</v>
       </c>
       <c r="E262" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F262" t="s">
-        <v>1058</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -7216,10 +7366,10 @@
         <v>267</v>
       </c>
       <c r="E263" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F263" t="s">
-        <v>1059</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -7227,10 +7377,10 @@
         <v>268</v>
       </c>
       <c r="E264" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F264" t="s">
-        <v>1060</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7238,10 +7388,10 @@
         <v>269</v>
       </c>
       <c r="E265" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F265" t="s">
-        <v>1061</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7249,10 +7399,10 @@
         <v>270</v>
       </c>
       <c r="E266" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F266" t="s">
-        <v>1062</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7260,10 +7410,10 @@
         <v>271</v>
       </c>
       <c r="E267" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F267" t="s">
-        <v>1063</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7271,10 +7421,10 @@
         <v>272</v>
       </c>
       <c r="E268" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F268" t="s">
-        <v>1064</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7282,10 +7432,10 @@
         <v>273</v>
       </c>
       <c r="E269" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F269" t="s">
-        <v>1065</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7293,10 +7443,10 @@
         <v>274</v>
       </c>
       <c r="E270" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F270" t="s">
-        <v>1066</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7304,10 +7454,10 @@
         <v>275</v>
       </c>
       <c r="E271" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F271" t="s">
-        <v>1067</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7315,10 +7465,10 @@
         <v>276</v>
       </c>
       <c r="E272" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F272" t="s">
-        <v>1068</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7326,10 +7476,10 @@
         <v>277</v>
       </c>
       <c r="E273" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F273" t="s">
-        <v>1069</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7337,10 +7487,10 @@
         <v>278</v>
       </c>
       <c r="E274" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F274" t="s">
-        <v>1070</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7348,10 +7498,10 @@
         <v>279</v>
       </c>
       <c r="E275" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F275" t="s">
-        <v>1071</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7359,10 +7509,10 @@
         <v>280</v>
       </c>
       <c r="E276" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F276" t="s">
-        <v>1072</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7370,10 +7520,10 @@
         <v>281</v>
       </c>
       <c r="E277" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F277" t="s">
-        <v>1073</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7381,10 +7531,10 @@
         <v>282</v>
       </c>
       <c r="E278" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F278" t="s">
-        <v>1074</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7392,10 +7542,10 @@
         <v>283</v>
       </c>
       <c r="E279" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F279" t="s">
-        <v>1075</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7403,10 +7553,10 @@
         <v>284</v>
       </c>
       <c r="E280" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F280" t="s">
-        <v>1076</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7414,10 +7564,10 @@
         <v>285</v>
       </c>
       <c r="E281" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F281" t="s">
-        <v>1077</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7425,10 +7575,10 @@
         <v>286</v>
       </c>
       <c r="E282" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F282" t="s">
-        <v>1078</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7436,10 +7586,10 @@
         <v>287</v>
       </c>
       <c r="E283" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F283" t="s">
-        <v>1079</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -7447,16 +7597,16 @@
         <v>288</v>
       </c>
       <c r="B284" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="C284" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D284" t="s">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="E284" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F284" t="s">
         <v>288</v>
@@ -7467,19 +7617,19 @@
         <v>289</v>
       </c>
       <c r="B285" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="C285" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D285" t="s">
-        <v>697</v>
+        <v>722</v>
       </c>
       <c r="E285" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F285" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -7487,16 +7637,16 @@
         <v>290</v>
       </c>
       <c r="B286" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="C286" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D286" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="E286" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F286" t="s">
         <v>290</v>
@@ -7507,19 +7657,19 @@
         <v>291</v>
       </c>
       <c r="B287" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="C287" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D287" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="E287" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F287" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7527,19 +7677,19 @@
         <v>292</v>
       </c>
       <c r="B288" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="C288" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D288" t="s">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="E288" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F288" t="s">
-        <v>1082</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -7547,10 +7697,10 @@
         <v>293</v>
       </c>
       <c r="E289" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F289" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -7558,16 +7708,16 @@
         <v>294</v>
       </c>
       <c r="B290" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="C290" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D290" t="s">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="E290" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F290" t="s">
         <v>294</v>
@@ -7578,16 +7728,16 @@
         <v>295</v>
       </c>
       <c r="B291" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="C291" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D291" t="s">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="E291" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F291" t="s">
         <v>295</v>
@@ -7598,10 +7748,10 @@
         <v>296</v>
       </c>
       <c r="E292" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F292" t="s">
-        <v>1084</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -7609,16 +7759,16 @@
         <v>297</v>
       </c>
       <c r="B293" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C293" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D293" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="E293" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F293" t="s">
         <v>297</v>
@@ -7629,16 +7779,16 @@
         <v>298</v>
       </c>
       <c r="B294" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="C294" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="E294" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F294" t="s">
-        <v>1085</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -7646,16 +7796,16 @@
         <v>299</v>
       </c>
       <c r="B295" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="C295" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E295" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F295" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -7663,19 +7813,19 @@
         <v>300</v>
       </c>
       <c r="B296" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C296" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D296" t="s">
-        <v>704</v>
+        <v>729</v>
       </c>
       <c r="E296" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F296" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -7683,19 +7833,19 @@
         <v>301</v>
       </c>
       <c r="B297" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="C297" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D297" t="s">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="E297" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F297" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -7703,10 +7853,10 @@
         <v>302</v>
       </c>
       <c r="E298" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F298" t="s">
-        <v>1089</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -7714,16 +7864,16 @@
         <v>303</v>
       </c>
       <c r="B299" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="C299" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="E299" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F299" t="s">
-        <v>1090</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -7731,13 +7881,13 @@
         <v>304</v>
       </c>
       <c r="B300" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="E300" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F300" t="s">
-        <v>1091</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -7745,19 +7895,19 @@
         <v>305</v>
       </c>
       <c r="B301" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="C301" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D301" t="s">
-        <v>706</v>
+        <v>731</v>
       </c>
       <c r="E301" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F301" t="s">
-        <v>1092</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -7765,16 +7915,16 @@
         <v>306</v>
       </c>
       <c r="B302" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="C302" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D302" t="s">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="E302" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F302" t="s">
         <v>306</v>
@@ -7785,19 +7935,19 @@
         <v>307</v>
       </c>
       <c r="B303" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="C303" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D303" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="E303" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F303" t="s">
-        <v>1093</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -7805,10 +7955,10 @@
         <v>308</v>
       </c>
       <c r="E304" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F304" t="s">
-        <v>1094</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -7816,16 +7966,16 @@
         <v>309</v>
       </c>
       <c r="B305" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="C305" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D305" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="E305" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F305" t="s">
         <v>309</v>
@@ -7836,16 +7986,16 @@
         <v>310</v>
       </c>
       <c r="B306" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="C306" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D306" t="s">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="E306" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F306" t="s">
         <v>310</v>
@@ -7856,19 +8006,19 @@
         <v>311</v>
       </c>
       <c r="B307" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="C307" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D307" t="s">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="E307" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F307" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -7876,16 +8026,16 @@
         <v>312</v>
       </c>
       <c r="B308" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="C308" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D308" t="s">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="E308" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F308" t="s">
         <v>312</v>
@@ -7896,19 +8046,19 @@
         <v>313</v>
       </c>
       <c r="B309" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="C309" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D309" t="s">
-        <v>713</v>
+        <v>738</v>
       </c>
       <c r="E309" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F309" t="s">
-        <v>1096</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -7916,19 +8066,19 @@
         <v>314</v>
       </c>
       <c r="B310" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="C310" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D310" t="s">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="E310" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F310" t="s">
-        <v>1097</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -7936,19 +8086,19 @@
         <v>315</v>
       </c>
       <c r="B311" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="C311" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D311" t="s">
-        <v>715</v>
+        <v>740</v>
       </c>
       <c r="E311" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F311" t="s">
-        <v>1098</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -7956,10 +8106,10 @@
         <v>316</v>
       </c>
       <c r="E312" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F312" t="s">
-        <v>1099</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -7967,16 +8117,16 @@
         <v>317</v>
       </c>
       <c r="B313" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="C313" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="E313" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F313" t="s">
-        <v>1100</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -7984,16 +8134,16 @@
         <v>318</v>
       </c>
       <c r="B314" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="C314" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="E314" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F314" t="s">
-        <v>1101</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -8001,10 +8151,10 @@
         <v>319</v>
       </c>
       <c r="E315" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F315" t="s">
-        <v>1102</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -8012,19 +8162,19 @@
         <v>320</v>
       </c>
       <c r="B316" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="C316" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D316" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="E316" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F316" t="s">
-        <v>1103</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -8032,19 +8182,19 @@
         <v>321</v>
       </c>
       <c r="B317" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="C317" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D317" t="s">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="E317" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F317" t="s">
-        <v>1104</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -8052,10 +8202,10 @@
         <v>322</v>
       </c>
       <c r="E318" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F318" t="s">
-        <v>1105</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -8063,19 +8213,19 @@
         <v>323</v>
       </c>
       <c r="B319" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="C319" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D319" t="s">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="E319" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F319" t="s">
-        <v>1106</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -8083,10 +8233,10 @@
         <v>324</v>
       </c>
       <c r="E320" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F320" t="s">
-        <v>1107</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -8094,10 +8244,10 @@
         <v>325</v>
       </c>
       <c r="E321" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F321" t="s">
-        <v>1108</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -8105,19 +8255,19 @@
         <v>326</v>
       </c>
       <c r="B322" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="C322" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D322" t="s">
-        <v>719</v>
+        <v>744</v>
       </c>
       <c r="E322" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F322" t="s">
-        <v>1109</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -8125,10 +8275,10 @@
         <v>327</v>
       </c>
       <c r="E323" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F323" t="s">
-        <v>1110</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -8136,19 +8286,19 @@
         <v>328</v>
       </c>
       <c r="B324" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C324" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D324" t="s">
-        <v>720</v>
+        <v>745</v>
       </c>
       <c r="E324" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F324" t="s">
-        <v>1111</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -8156,19 +8306,19 @@
         <v>329</v>
       </c>
       <c r="B325" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="C325" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D325" t="s">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="E325" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F325" t="s">
-        <v>1112</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -8176,13 +8326,13 @@
         <v>330</v>
       </c>
       <c r="B326" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="E326" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F326" t="s">
-        <v>1113</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -8190,19 +8340,19 @@
         <v>331</v>
       </c>
       <c r="B327" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="C327" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D327" t="s">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="E327" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F327" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -8210,19 +8360,19 @@
         <v>332</v>
       </c>
       <c r="B328" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="C328" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D328" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="E328" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F328" t="s">
-        <v>1115</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8230,16 +8380,16 @@
         <v>333</v>
       </c>
       <c r="B329" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="C329" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D329" t="s">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="E329" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F329" t="s">
         <v>333</v>
@@ -8250,13 +8400,13 @@
         <v>334</v>
       </c>
       <c r="B330" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="E330" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F330" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -8264,19 +8414,19 @@
         <v>335</v>
       </c>
       <c r="B331" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="C331" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D331" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="E331" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F331" t="s">
-        <v>1117</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -8284,16 +8434,16 @@
         <v>336</v>
       </c>
       <c r="B332" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="C332" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D332" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="E332" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F332" t="s">
         <v>336</v>
@@ -8304,19 +8454,19 @@
         <v>337</v>
       </c>
       <c r="B333" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C333" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D333" t="s">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="E333" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F333" t="s">
-        <v>1118</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -8324,19 +8474,19 @@
         <v>338</v>
       </c>
       <c r="B334" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="C334" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D334" t="s">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="E334" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F334" t="s">
-        <v>1119</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -8344,10 +8494,10 @@
         <v>339</v>
       </c>
       <c r="E335" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F335" t="s">
-        <v>1120</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -8355,13 +8505,13 @@
         <v>340</v>
       </c>
       <c r="B336" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="E336" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F336" t="s">
-        <v>1121</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -8369,19 +8519,19 @@
         <v>341</v>
       </c>
       <c r="B337" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="C337" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D337" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="E337" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F337" t="s">
-        <v>1122</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -8389,13 +8539,13 @@
         <v>342</v>
       </c>
       <c r="B338" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="E338" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F338" t="s">
-        <v>1123</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -8403,16 +8553,16 @@
         <v>343</v>
       </c>
       <c r="B339" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="C339" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D339" t="s">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="E339" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F339" t="s">
         <v>343</v>
@@ -8423,10 +8573,10 @@
         <v>344</v>
       </c>
       <c r="E340" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F340" t="s">
-        <v>1124</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -8434,10 +8584,10 @@
         <v>345</v>
       </c>
       <c r="E341" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F341" t="s">
-        <v>1125</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -8445,13 +8595,13 @@
         <v>346</v>
       </c>
       <c r="B342" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="E342" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F342" t="s">
-        <v>1126</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -8459,19 +8609,19 @@
         <v>347</v>
       </c>
       <c r="B343" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="C343" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D343" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="E343" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F343" t="s">
-        <v>1127</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -8479,19 +8629,19 @@
         <v>348</v>
       </c>
       <c r="B344" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="C344" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D344" t="s">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="E344" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F344" t="s">
-        <v>1128</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -8499,19 +8649,19 @@
         <v>349</v>
       </c>
       <c r="B345" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="C345" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D345" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="E345" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F345" t="s">
-        <v>1129</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -8519,19 +8669,19 @@
         <v>350</v>
       </c>
       <c r="B346" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="C346" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D346" t="s">
-        <v>733</v>
+        <v>758</v>
       </c>
       <c r="E346" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F346" t="s">
-        <v>1130</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -8539,10 +8689,10 @@
         <v>351</v>
       </c>
       <c r="E347" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F347" t="s">
-        <v>1131</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -8550,19 +8700,19 @@
         <v>352</v>
       </c>
       <c r="B348" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="C348" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D348" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="E348" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F348" t="s">
-        <v>1132</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -8570,16 +8720,16 @@
         <v>353</v>
       </c>
       <c r="B349" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="C349" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D349" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="E349" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F349" t="s">
         <v>353</v>
@@ -8590,16 +8740,16 @@
         <v>354</v>
       </c>
       <c r="B350" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="C350" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D350" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
       <c r="E350" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F350" t="s">
         <v>354</v>
@@ -8610,16 +8760,16 @@
         <v>355</v>
       </c>
       <c r="B351" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="C351" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D351" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="E351" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F351" t="s">
         <v>355</v>
@@ -8630,16 +8780,16 @@
         <v>356</v>
       </c>
       <c r="B352" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="C352" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D352" t="s">
-        <v>738</v>
+        <v>763</v>
       </c>
       <c r="E352" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F352" t="s">
         <v>356</v>
@@ -8650,19 +8800,19 @@
         <v>357</v>
       </c>
       <c r="B353" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="C353" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D353" t="s">
-        <v>739</v>
+        <v>764</v>
       </c>
       <c r="E353" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F353" t="s">
-        <v>1133</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -8670,19 +8820,19 @@
         <v>358</v>
       </c>
       <c r="B354" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="C354" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D354" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="E354" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F354" t="s">
-        <v>1134</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -8690,19 +8840,19 @@
         <v>359</v>
       </c>
       <c r="B355" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="C355" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D355" t="s">
-        <v>741</v>
+        <v>766</v>
       </c>
       <c r="E355" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F355" t="s">
-        <v>1135</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -8710,19 +8860,19 @@
         <v>360</v>
       </c>
       <c r="B356" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="C356" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D356" t="s">
-        <v>742</v>
+        <v>767</v>
       </c>
       <c r="E356" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F356" t="s">
-        <v>1136</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -8730,10 +8880,10 @@
         <v>361</v>
       </c>
       <c r="E357" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F357" t="s">
-        <v>1137</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -8741,19 +8891,19 @@
         <v>362</v>
       </c>
       <c r="B358" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="C358" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D358" t="s">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="E358" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F358" t="s">
-        <v>1138</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="359" spans="1:6">
@@ -8761,16 +8911,16 @@
         <v>363</v>
       </c>
       <c r="B359" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="C359" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E359" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F359" t="s">
-        <v>1139</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -8778,16 +8928,16 @@
         <v>364</v>
       </c>
       <c r="B360" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="C360" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E360" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F360" t="s">
-        <v>1140</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -8795,16 +8945,16 @@
         <v>365</v>
       </c>
       <c r="B361" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="C361" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="D361" t="s">
-        <v>744</v>
+        <v>769</v>
       </c>
       <c r="E361" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F361" t="s">
         <v>365</v>
@@ -8815,19 +8965,19 @@
         <v>366</v>
       </c>
       <c r="B362" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="C362" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D362" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
       <c r="E362" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F362" t="s">
-        <v>1141</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -8835,13 +8985,13 @@
         <v>367</v>
       </c>
       <c r="C363" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E363" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F363" t="s">
-        <v>1142</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -8849,13 +8999,13 @@
         <v>368</v>
       </c>
       <c r="C364" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E364" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F364" t="s">
-        <v>1143</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="365" spans="1:6">
@@ -8863,13 +9013,13 @@
         <v>369</v>
       </c>
       <c r="C365" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E365" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F365" t="s">
-        <v>1144</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -8877,16 +9027,16 @@
         <v>370</v>
       </c>
       <c r="B366" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="C366" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D366" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="E366" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F366" t="s">
         <v>370</v>
@@ -8897,16 +9047,16 @@
         <v>371</v>
       </c>
       <c r="B367" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C367" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="D367" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
       <c r="E367" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F367" t="s">
         <v>371</v>
@@ -8917,19 +9067,19 @@
         <v>372</v>
       </c>
       <c r="B368" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="C368" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D368" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="E368" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F368" t="s">
-        <v>1145</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="369" spans="1:6">
@@ -8937,13 +9087,13 @@
         <v>373</v>
       </c>
       <c r="B369" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="E369" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F369" t="s">
-        <v>1146</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -8951,13 +9101,13 @@
         <v>374</v>
       </c>
       <c r="C370" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E370" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F370" t="s">
-        <v>1147</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -8965,16 +9115,16 @@
         <v>375</v>
       </c>
       <c r="B371" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="C371" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D371" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="E371" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F371" t="s">
         <v>375</v>
@@ -8985,16 +9135,16 @@
         <v>376</v>
       </c>
       <c r="B372" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C372" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D372" t="s">
-        <v>748</v>
+        <v>773</v>
       </c>
       <c r="E372" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F372" t="s">
         <v>376</v>
@@ -9005,16 +9155,16 @@
         <v>377</v>
       </c>
       <c r="B373" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="C373" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D373" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="E373" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F373" t="s">
         <v>377</v>
@@ -9025,16 +9175,16 @@
         <v>378</v>
       </c>
       <c r="B374" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="C374" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D374" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="E374" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F374" t="s">
         <v>378</v>
@@ -9045,16 +9195,16 @@
         <v>379</v>
       </c>
       <c r="B375" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="C375" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D375" t="s">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="E375" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F375" t="s">
         <v>379</v>
@@ -9065,16 +9215,16 @@
         <v>380</v>
       </c>
       <c r="B376" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="C376" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D376" t="s">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="E376" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F376" t="s">
         <v>380</v>
@@ -9085,19 +9235,19 @@
         <v>381</v>
       </c>
       <c r="B377" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="C377" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D377" t="s">
-        <v>752</v>
+        <v>777</v>
       </c>
       <c r="E377" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F377" t="s">
-        <v>1148</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -9105,19 +9255,19 @@
         <v>382</v>
       </c>
       <c r="B378" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="C378" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D378" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="E378" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F378" t="s">
-        <v>1149</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -9125,16 +9275,16 @@
         <v>383</v>
       </c>
       <c r="B379" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="C379" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D379" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
       <c r="E379" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F379" t="s">
         <v>383</v>
@@ -9145,19 +9295,19 @@
         <v>384</v>
       </c>
       <c r="B380" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="C380" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D380" t="s">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="E380" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F380" t="s">
-        <v>1150</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -9165,16 +9315,16 @@
         <v>385</v>
       </c>
       <c r="B381" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="C381" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D381" t="s">
-        <v>756</v>
+        <v>781</v>
       </c>
       <c r="E381" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F381" t="s">
         <v>385</v>
@@ -9185,19 +9335,19 @@
         <v>386</v>
       </c>
       <c r="B382" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="C382" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D382" t="s">
-        <v>757</v>
+        <v>782</v>
       </c>
       <c r="E382" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F382" t="s">
-        <v>1151</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -9205,19 +9355,19 @@
         <v>387</v>
       </c>
       <c r="B383" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="C383" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D383" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="E383" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F383" t="s">
-        <v>1152</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -9225,19 +9375,19 @@
         <v>388</v>
       </c>
       <c r="B384" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="C384" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="D384" t="s">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="E384" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F384" t="s">
-        <v>1153</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -9245,10 +9395,10 @@
         <v>389</v>
       </c>
       <c r="E385" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F385" t="s">
-        <v>1154</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -9256,10 +9406,10 @@
         <v>390</v>
       </c>
       <c r="E386" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F386" t="s">
-        <v>1155</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -9267,16 +9417,16 @@
         <v>391</v>
       </c>
       <c r="B387" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="C387" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E387" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F387" t="s">
-        <v>1156</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -9284,19 +9434,19 @@
         <v>392</v>
       </c>
       <c r="B388" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="C388" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D388" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
       <c r="E388" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F388" t="s">
-        <v>1157</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -9304,19 +9454,19 @@
         <v>393</v>
       </c>
       <c r="B389" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="C389" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D389" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="E389" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F389" t="s">
-        <v>1158</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -9324,19 +9474,19 @@
         <v>394</v>
       </c>
       <c r="B390" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="C390" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D390" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="E390" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F390" t="s">
-        <v>1159</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -9344,19 +9494,19 @@
         <v>395</v>
       </c>
       <c r="B391" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="C391" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D391" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="E391" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F391" t="s">
-        <v>1160</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -9364,19 +9514,19 @@
         <v>396</v>
       </c>
       <c r="B392" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="C392" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D392" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="E392" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F392" t="s">
-        <v>1161</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -9384,19 +9534,19 @@
         <v>397</v>
       </c>
       <c r="B393" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="C393" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D393" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="E393" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F393" t="s">
-        <v>1162</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -9404,19 +9554,19 @@
         <v>398</v>
       </c>
       <c r="B394" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="C394" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D394" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="E394" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F394" t="s">
-        <v>1163</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="395" spans="1:6">
@@ -9424,16 +9574,16 @@
         <v>399</v>
       </c>
       <c r="B395" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="C395" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D395" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="E395" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F395" t="s">
         <v>399</v>
@@ -9444,16 +9594,16 @@
         <v>400</v>
       </c>
       <c r="B396" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="C396" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D396" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="E396" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F396" t="s">
         <v>400</v>
@@ -9464,16 +9614,16 @@
         <v>401</v>
       </c>
       <c r="B397" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="C397" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D397" t="s">
-        <v>763</v>
+        <v>788</v>
       </c>
       <c r="E397" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F397" t="s">
         <v>401</v>
@@ -9484,19 +9634,19 @@
         <v>402</v>
       </c>
       <c r="B398" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="C398" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D398" t="s">
-        <v>764</v>
+        <v>789</v>
       </c>
       <c r="E398" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F398" t="s">
-        <v>1164</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="399" spans="1:6">
@@ -9504,19 +9654,19 @@
         <v>403</v>
       </c>
       <c r="B399" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="C399" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D399" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="E399" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F399" t="s">
-        <v>1165</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -9524,19 +9674,19 @@
         <v>404</v>
       </c>
       <c r="B400" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="C400" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D400" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="E400" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F400" t="s">
-        <v>1166</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -9544,19 +9694,19 @@
         <v>405</v>
       </c>
       <c r="B401" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="C401" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D401" t="s">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="E401" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F401" t="s">
-        <v>1167</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -9564,19 +9714,19 @@
         <v>406</v>
       </c>
       <c r="B402" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="C402" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D402" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="E402" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F402" t="s">
-        <v>1168</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="403" spans="1:6">
@@ -9584,16 +9734,16 @@
         <v>407</v>
       </c>
       <c r="B403" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="C403" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="E403" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F403" t="s">
-        <v>1169</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -9601,19 +9751,19 @@
         <v>408</v>
       </c>
       <c r="B404" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="C404" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D404" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
       <c r="E404" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F404" t="s">
-        <v>1170</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -9621,19 +9771,19 @@
         <v>409</v>
       </c>
       <c r="B405" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="C405" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D405" t="s">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="E405" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F405" t="s">
-        <v>1171</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -9641,16 +9791,16 @@
         <v>410</v>
       </c>
       <c r="B406" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="C406" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="E406" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F406" t="s">
-        <v>1172</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -9658,16 +9808,16 @@
         <v>411</v>
       </c>
       <c r="B407" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="C407" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="E407" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F407" t="s">
-        <v>1173</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9675,16 +9825,16 @@
         <v>412</v>
       </c>
       <c r="B408" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="C408" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E408" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F408" t="s">
-        <v>1174</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -9692,16 +9842,16 @@
         <v>413</v>
       </c>
       <c r="B409" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="C409" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E409" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F409" t="s">
-        <v>1175</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -9709,19 +9859,19 @@
         <v>414</v>
       </c>
       <c r="B410" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="C410" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D410" t="s">
-        <v>771</v>
+        <v>796</v>
       </c>
       <c r="E410" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F410" t="s">
-        <v>1176</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -9729,19 +9879,19 @@
         <v>415</v>
       </c>
       <c r="B411" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="C411" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="D411" t="s">
-        <v>772</v>
+        <v>797</v>
       </c>
       <c r="E411" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F411" t="s">
-        <v>1177</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -9749,19 +9899,19 @@
         <v>416</v>
       </c>
       <c r="B412" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="C412" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="D412" t="s">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="E412" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F412" t="s">
-        <v>1178</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9769,19 +9919,19 @@
         <v>417</v>
       </c>
       <c r="B413" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="C413" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D413" t="s">
-        <v>774</v>
+        <v>799</v>
       </c>
       <c r="E413" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F413" t="s">
-        <v>1179</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -9789,19 +9939,19 @@
         <v>418</v>
       </c>
       <c r="B414" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="C414" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D414" t="s">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="E414" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F414" t="s">
-        <v>1180</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -9809,16 +9959,16 @@
         <v>419</v>
       </c>
       <c r="B415" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="C415" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="E415" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F415" t="s">
-        <v>1181</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -9826,16 +9976,16 @@
         <v>420</v>
       </c>
       <c r="B416" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="C416" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D416" t="s">
-        <v>776</v>
+        <v>801</v>
       </c>
       <c r="E416" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F416" t="s">
         <v>420</v>
@@ -9846,16 +9996,16 @@
         <v>421</v>
       </c>
       <c r="B417" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="C417" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E417" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F417" t="s">
-        <v>1182</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -9863,16 +10013,16 @@
         <v>422</v>
       </c>
       <c r="B418" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="C418" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E418" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F418" t="s">
-        <v>1183</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -9880,16 +10030,16 @@
         <v>423</v>
       </c>
       <c r="B419" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="C419" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E419" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F419" t="s">
-        <v>1184</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -9897,16 +10047,16 @@
         <v>424</v>
       </c>
       <c r="B420" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="C420" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E420" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F420" t="s">
-        <v>1185</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -9914,16 +10064,16 @@
         <v>425</v>
       </c>
       <c r="B421" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="C421" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E421" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F421" t="s">
-        <v>1186</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -9931,10 +10081,10 @@
         <v>426</v>
       </c>
       <c r="E422" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F422" t="s">
-        <v>1187</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -9942,10 +10092,10 @@
         <v>427</v>
       </c>
       <c r="E423" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F423" t="s">
-        <v>1188</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -9953,10 +10103,10 @@
         <v>428</v>
       </c>
       <c r="E424" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F424" t="s">
-        <v>1189</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="425" spans="1:6">
@@ -9964,10 +10114,10 @@
         <v>429</v>
       </c>
       <c r="E425" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F425" t="s">
-        <v>1190</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="426" spans="1:6">
@@ -9975,10 +10125,10 @@
         <v>430</v>
       </c>
       <c r="E426" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F426" t="s">
-        <v>1191</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -9986,10 +10136,10 @@
         <v>431</v>
       </c>
       <c r="E427" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F427" t="s">
-        <v>1192</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -9997,19 +10147,19 @@
         <v>432</v>
       </c>
       <c r="B428" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="C428" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D428" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
       <c r="E428" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F428" t="s">
-        <v>1193</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -10017,10 +10167,10 @@
         <v>433</v>
       </c>
       <c r="E429" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F429" t="s">
-        <v>1194</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -10028,10 +10178,10 @@
         <v>434</v>
       </c>
       <c r="E430" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F430" t="s">
-        <v>1195</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -10039,10 +10189,10 @@
         <v>435</v>
       </c>
       <c r="E431" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F431" t="s">
-        <v>1196</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -10050,10 +10200,10 @@
         <v>436</v>
       </c>
       <c r="E432" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F432" t="s">
-        <v>1197</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -10061,10 +10211,10 @@
         <v>437</v>
       </c>
       <c r="E433" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F433" t="s">
-        <v>1198</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -10072,19 +10222,19 @@
         <v>438</v>
       </c>
       <c r="B434" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="C434" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D434" t="s">
-        <v>778</v>
+        <v>803</v>
       </c>
       <c r="E434" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F434" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -10092,16 +10242,16 @@
         <v>439</v>
       </c>
       <c r="B435" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="C435" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D435" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="E435" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F435" t="s">
         <v>439</v>
@@ -10112,19 +10262,19 @@
         <v>440</v>
       </c>
       <c r="B436" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="C436" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D436" t="s">
-        <v>780</v>
+        <v>805</v>
       </c>
       <c r="E436" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F436" t="s">
-        <v>1200</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -10132,16 +10282,16 @@
         <v>441</v>
       </c>
       <c r="B437" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="C437" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E437" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F437" t="s">
-        <v>1201</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -10149,16 +10299,16 @@
         <v>442</v>
       </c>
       <c r="B438" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="C438" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E438" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F438" t="s">
-        <v>1202</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -10166,16 +10316,16 @@
         <v>443</v>
       </c>
       <c r="B439" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="C439" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E439" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F439" t="s">
-        <v>1203</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="440" spans="1:6">
@@ -10183,16 +10333,16 @@
         <v>444</v>
       </c>
       <c r="B440" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="C440" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E440" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F440" t="s">
-        <v>1204</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -10200,13 +10350,13 @@
         <v>445</v>
       </c>
       <c r="B441" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="E441" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F441" t="s">
-        <v>1205</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="442" spans="1:6">
@@ -10214,19 +10364,19 @@
         <v>446</v>
       </c>
       <c r="B442" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="C442" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D442" t="s">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="E442" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F442" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -10234,16 +10384,16 @@
         <v>447</v>
       </c>
       <c r="B443" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="C443" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="E443" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F443" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -10251,19 +10401,19 @@
         <v>448</v>
       </c>
       <c r="B444" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="C444" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D444" t="s">
-        <v>782</v>
+        <v>807</v>
       </c>
       <c r="E444" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F444" t="s">
-        <v>1208</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -10271,10 +10421,10 @@
         <v>449</v>
       </c>
       <c r="E445" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F445" t="s">
-        <v>1209</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -10282,10 +10432,10 @@
         <v>450</v>
       </c>
       <c r="E446" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F446" t="s">
-        <v>1210</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -10293,16 +10443,16 @@
         <v>451</v>
       </c>
       <c r="B447" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="C447" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D447" t="s">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="E447" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F447" t="s">
         <v>451</v>
@@ -10313,16 +10463,16 @@
         <v>452</v>
       </c>
       <c r="B448" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="C448" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D448" t="s">
-        <v>783</v>
+        <v>808</v>
       </c>
       <c r="E448" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F448" t="s">
         <v>452</v>
@@ -10333,16 +10483,16 @@
         <v>453</v>
       </c>
       <c r="B449" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="C449" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D449" t="s">
-        <v>784</v>
+        <v>809</v>
       </c>
       <c r="E449" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F449" t="s">
         <v>453</v>
@@ -10353,16 +10503,16 @@
         <v>454</v>
       </c>
       <c r="B450" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="C450" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D450" t="s">
-        <v>785</v>
+        <v>810</v>
       </c>
       <c r="E450" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F450" t="s">
         <v>454</v>
@@ -10373,19 +10523,19 @@
         <v>455</v>
       </c>
       <c r="B451" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="C451" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D451" t="s">
-        <v>786</v>
+        <v>811</v>
       </c>
       <c r="E451" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F451" t="s">
-        <v>1211</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="452" spans="1:6">
@@ -10393,16 +10543,16 @@
         <v>456</v>
       </c>
       <c r="B452" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="C452" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D452" t="s">
-        <v>786</v>
+        <v>811</v>
       </c>
       <c r="E452" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F452" t="s">
         <v>456</v>
@@ -10413,19 +10563,19 @@
         <v>457</v>
       </c>
       <c r="B453" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="C453" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D453" t="s">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="E453" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F453" t="s">
-        <v>1212</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="454" spans="1:6">
@@ -10433,10 +10583,10 @@
         <v>458</v>
       </c>
       <c r="E454" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F454" t="s">
-        <v>1213</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -10444,19 +10594,19 @@
         <v>459</v>
       </c>
       <c r="B455" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="C455" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D455" t="s">
-        <v>788</v>
+        <v>813</v>
       </c>
       <c r="E455" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F455" t="s">
-        <v>1214</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="456" spans="1:6">
@@ -10464,19 +10614,19 @@
         <v>460</v>
       </c>
       <c r="B456" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="C456" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D456" t="s">
-        <v>789</v>
+        <v>814</v>
       </c>
       <c r="E456" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F456" t="s">
-        <v>1215</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="457" spans="1:6">
@@ -10484,16 +10634,16 @@
         <v>461</v>
       </c>
       <c r="B457" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="C457" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E457" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F457" t="s">
-        <v>1216</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="458" spans="1:6">
@@ -10501,16 +10651,16 @@
         <v>462</v>
       </c>
       <c r="B458" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="C458" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E458" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F458" t="s">
-        <v>1217</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -10518,16 +10668,16 @@
         <v>463</v>
       </c>
       <c r="B459" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="C459" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E459" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F459" t="s">
-        <v>1218</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="460" spans="1:6">
@@ -10535,16 +10685,16 @@
         <v>464</v>
       </c>
       <c r="B460" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="C460" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E460" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F460" t="s">
-        <v>1219</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="461" spans="1:6">
@@ -10552,16 +10702,16 @@
         <v>465</v>
       </c>
       <c r="B461" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="C461" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E461" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F461" t="s">
-        <v>1220</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="462" spans="1:6">
@@ -10569,16 +10719,16 @@
         <v>466</v>
       </c>
       <c r="B462" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="C462" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E462" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F462" t="s">
-        <v>1221</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="463" spans="1:6">
@@ -10586,16 +10736,16 @@
         <v>467</v>
       </c>
       <c r="B463" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="C463" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E463" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F463" t="s">
-        <v>1222</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="464" spans="1:6">
@@ -10603,16 +10753,16 @@
         <v>468</v>
       </c>
       <c r="B464" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="C464" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E464" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F464" t="s">
-        <v>1223</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -10620,16 +10770,16 @@
         <v>469</v>
       </c>
       <c r="B465" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="C465" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E465" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F465" t="s">
-        <v>1224</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -10637,16 +10787,16 @@
         <v>470</v>
       </c>
       <c r="B466" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="C466" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E466" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F466" t="s">
-        <v>1225</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -10654,10 +10804,10 @@
         <v>471</v>
       </c>
       <c r="E467" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F467" t="s">
-        <v>1226</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="468" spans="1:6">
@@ -10665,10 +10815,10 @@
         <v>472</v>
       </c>
       <c r="E468" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F468" t="s">
-        <v>1227</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="469" spans="1:6">
@@ -10676,10 +10826,10 @@
         <v>473</v>
       </c>
       <c r="E469" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F469" t="s">
-        <v>1228</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="470" spans="1:6">
@@ -10687,10 +10837,10 @@
         <v>474</v>
       </c>
       <c r="E470" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F470" t="s">
-        <v>1229</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -10698,10 +10848,10 @@
         <v>475</v>
       </c>
       <c r="E471" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F471" t="s">
-        <v>1230</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -10709,19 +10859,19 @@
         <v>476</v>
       </c>
       <c r="B472" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="C472" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D472" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="E472" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F472" t="s">
-        <v>1231</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -10729,16 +10879,16 @@
         <v>477</v>
       </c>
       <c r="B473" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="C473" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D473" t="s">
-        <v>791</v>
+        <v>816</v>
       </c>
       <c r="E473" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F473" t="s">
         <v>477</v>
@@ -10749,16 +10899,16 @@
         <v>478</v>
       </c>
       <c r="B474" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="C474" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D474" t="s">
-        <v>792</v>
+        <v>817</v>
       </c>
       <c r="E474" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F474" t="s">
         <v>478</v>
@@ -10769,16 +10919,16 @@
         <v>479</v>
       </c>
       <c r="B475" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="C475" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D475" t="s">
-        <v>793</v>
+        <v>818</v>
       </c>
       <c r="E475" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F475" t="s">
         <v>479</v>
@@ -10789,19 +10939,19 @@
         <v>480</v>
       </c>
       <c r="B476" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="C476" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D476" t="s">
-        <v>794</v>
+        <v>819</v>
       </c>
       <c r="E476" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F476" t="s">
-        <v>1232</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -10809,19 +10959,19 @@
         <v>481</v>
       </c>
       <c r="B477" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="C477" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="D477" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="E477" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F477" t="s">
-        <v>1233</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="478" spans="1:6">
@@ -10829,16 +10979,16 @@
         <v>482</v>
       </c>
       <c r="B478" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="C478" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D478" t="s">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="E478" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F478" t="s">
         <v>482</v>
@@ -10849,16 +10999,16 @@
         <v>483</v>
       </c>
       <c r="B479" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="C479" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D479" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="E479" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F479" t="s">
         <v>483</v>
@@ -10869,19 +11019,19 @@
         <v>484</v>
       </c>
       <c r="B480" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="C480" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D480" t="s">
-        <v>798</v>
+        <v>823</v>
       </c>
       <c r="E480" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F480" t="s">
-        <v>1234</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="481" spans="1:6">
@@ -10889,16 +11039,16 @@
         <v>485</v>
       </c>
       <c r="B481" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="C481" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D481" t="s">
-        <v>799</v>
+        <v>824</v>
       </c>
       <c r="E481" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F481" t="s">
         <v>485</v>
@@ -10909,10 +11059,10 @@
         <v>486</v>
       </c>
       <c r="E482" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F482" t="s">
-        <v>1235</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -10920,10 +11070,10 @@
         <v>487</v>
       </c>
       <c r="E483" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F483" t="s">
-        <v>1236</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="484" spans="1:6">
@@ -10931,19 +11081,19 @@
         <v>488</v>
       </c>
       <c r="B484" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="C484" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="D484" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="E484" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="F484" t="s">
-        <v>1237</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -10951,19 +11101,19 @@
         <v>489</v>
       </c>
       <c r="B485" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="C485" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D485" t="s">
-        <v>801</v>
+        <v>826</v>
       </c>
       <c r="E485" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F485" t="s">
-        <v>1238</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="486" spans="1:6">
@@ -10971,16 +11121,16 @@
         <v>490</v>
       </c>
       <c r="B486" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="C486" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="D486" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="E486" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F486" t="s">
         <v>490</v>
@@ -10991,10 +11141,210 @@
         <v>491</v>
       </c>
       <c r="E487" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F487" t="s">
-        <v>1239</v>
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6">
+      <c r="A488" t="s">
+        <v>492</v>
+      </c>
+      <c r="F488" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6">
+      <c r="A489" t="s">
+        <v>493</v>
+      </c>
+      <c r="F489" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6">
+      <c r="A490" t="s">
+        <v>494</v>
+      </c>
+      <c r="F490" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6">
+      <c r="A491" t="s">
+        <v>495</v>
+      </c>
+      <c r="F491" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6">
+      <c r="A492" t="s">
+        <v>496</v>
+      </c>
+      <c r="F492" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6">
+      <c r="A493" t="s">
+        <v>497</v>
+      </c>
+      <c r="F493" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6">
+      <c r="A494" t="s">
+        <v>498</v>
+      </c>
+      <c r="F494" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6">
+      <c r="A495" t="s">
+        <v>499</v>
+      </c>
+      <c r="F495" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6">
+      <c r="A496" t="s">
+        <v>500</v>
+      </c>
+      <c r="F496" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
+      <c r="A497" t="s">
+        <v>501</v>
+      </c>
+      <c r="F497" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
+      <c r="A498" t="s">
+        <v>502</v>
+      </c>
+      <c r="F498" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
+      <c r="A499" t="s">
+        <v>503</v>
+      </c>
+      <c r="F499" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
+      <c r="A500" t="s">
+        <v>504</v>
+      </c>
+      <c r="F500" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
+      <c r="A501" t="s">
+        <v>505</v>
+      </c>
+      <c r="F501" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
+      <c r="A502" t="s">
+        <v>506</v>
+      </c>
+      <c r="F502" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
+      <c r="A503" t="s">
+        <v>507</v>
+      </c>
+      <c r="F503" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504" t="s">
+        <v>508</v>
+      </c>
+      <c r="F504" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
+      <c r="A505" t="s">
+        <v>509</v>
+      </c>
+      <c r="F505" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506" t="s">
+        <v>510</v>
+      </c>
+      <c r="F506" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507" t="s">
+        <v>511</v>
+      </c>
+      <c r="F507" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508" t="s">
+        <v>512</v>
+      </c>
+      <c r="F508" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509" t="s">
+        <v>513</v>
+      </c>
+      <c r="F509" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510" t="s">
+        <v>514</v>
+      </c>
+      <c r="F510" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
+      <c r="A511" t="s">
+        <v>515</v>
+      </c>
+      <c r="F511" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512" t="s">
+        <v>516</v>
+      </c>
+      <c r="F512" t="s">
+        <v>1289</v>
       </c>
     </row>
   </sheetData>
